--- a/data/trans_dic/P2C_R1-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R1-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,54</t>
+          <t>1,15; 6,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,64</t>
+          <t>0,48; 4,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 22,11</t>
+          <t>7,23; 22,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,85</t>
+          <t>0,5; 5,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 8,13</t>
+          <t>1,48; 7,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,53</t>
+          <t>1,42; 6,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 20,53</t>
+          <t>6,88; 21,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,47</t>
+          <t>0,45; 2,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,7</t>
+          <t>1,88; 5,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,41</t>
+          <t>1,34; 4,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,69; 19,08</t>
+          <t>8,45; 19,25</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,0</t>
+          <t>0,84; 7,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,82</t>
+          <t>0,38; 3,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 21,81</t>
+          <t>6,06; 20,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,32</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,44</t>
+          <t>0,39; 3,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,72</t>
+          <t>0,42; 4,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,0; 23,33</t>
+          <t>9,87; 24,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,15</t>
+          <t>0,69; 4,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,5</t>
+          <t>0,38; 2,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,07</t>
+          <t>0,61; 3,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,48; 19,57</t>
+          <t>9,31; 19,47</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,29</t>
+          <t>0,24; 2,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,7</t>
+          <t>0,3; 3,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,19; 23,93</t>
+          <t>9,88; 23,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,19</t>
+          <t>0,0; 4,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,09; 41,82</t>
+          <t>18,6; 44,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,82</t>
+          <t>0,19; 1,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,82</t>
+          <t>0,32; 1,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,03</t>
+          <t>0,22; 1,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,09; 26,92</t>
+          <t>13,81; 26,07</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,72</t>
+          <t>0,16; 1,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,84; 25,34</t>
+          <t>14,01; 25,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,46</t>
+          <t>0,59; 3,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,08</t>
+          <t>0,55; 2,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,4</t>
+          <t>0,17; 1,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 11,68</t>
+          <t>1,07; 11,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,62</t>
+          <t>0,35; 1,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,29</t>
+          <t>0,22; 1,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,18</t>
+          <t>0,26; 1,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 16,43</t>
+          <t>3,6; 16,47</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,98</t>
+          <t>0,22; 2,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,68; 28,64</t>
+          <t>11,31; 27,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,4</t>
+          <t>0,36; 2,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,06</t>
+          <t>0,2; 2,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,24; 22,16</t>
+          <t>14,25; 22,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,87</t>
+          <t>0,38; 1,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,67</t>
+          <t>0,33; 1,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,53; 22,24</t>
+          <t>14,78; 22,34</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,91; 71,13</t>
+          <t>3,09; 58,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,93</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,42</t>
+          <t>0,14; 1,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,62</t>
+          <t>0,17; 1,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,66; 26,84</t>
+          <t>17,92; 27,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,11</t>
+          <t>0,12; 1,13</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,44</t>
+          <t>0,13; 1,34</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,84; 28,2</t>
+          <t>17,32; 27,06</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,08</t>
+          <t>0,28; 1,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,25</t>
+          <t>0,46; 1,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,5</t>
+          <t>0,54; 1,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,99; 20,11</t>
+          <t>13,57; 20,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,25</t>
+          <t>0,45; 1,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,61</t>
+          <t>0,74; 1,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,46</t>
+          <t>0,62; 1,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,6; 17,97</t>
+          <t>6,06; 17,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,99</t>
+          <t>0,44; 0,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,37</t>
+          <t>0,72; 1,34</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,31</t>
+          <t>0,68; 1,32</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,55; 17,67</t>
+          <t>8,56; 17,53</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6049</t>
+          <t>0; 5240</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2984; 16689</t>
+          <t>2946; 15632</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1037; 10178</t>
+          <t>1062; 9763</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4173; 13746</t>
+          <t>4497; 14176</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1042; 10018</t>
+          <t>1024; 11516</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3095; 16820</t>
+          <t>3066; 16440</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2857; 13494</t>
+          <t>2943; 13780</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4535; 14774</t>
+          <t>4952; 15630</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2187; 12043</t>
+          <t>2185; 12558</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8821; 26342</t>
+          <t>8703; 26189</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5841; 18793</t>
+          <t>5710; 18182</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11659; 25600</t>
+          <t>11340; 25823</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1610; 13760</t>
+          <t>1652; 13902</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 9704</t>
+          <t>0; 10443</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>889; 8731</t>
+          <t>871; 8326</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3338; 12679</t>
+          <t>3525; 11988</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 7425</t>
+          <t>0; 6915</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>908; 8164</t>
+          <t>925; 8257</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1021; 11501</t>
+          <t>1024; 10561</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6580; 15356</t>
+          <t>6496; 15808</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2853; 17444</t>
+          <t>2912; 16880</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1078; 12661</t>
+          <t>1921; 13713</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2887; 14503</t>
+          <t>2874; 14447</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11744; 24257</t>
+          <t>11544; 24134</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5983</t>
+          <t>0; 6209</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1837; 9384</t>
+          <t>991; 9006</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1002; 8909</t>
+          <t>1004; 10195</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7636; 19870</t>
+          <t>8203; 19738</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5279</t>
+          <t>0; 5757</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5794</t>
+          <t>0; 5252</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2116</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5493; 13443</t>
+          <t>5980; 14177</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>894; 8475</t>
+          <t>904; 8887</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1908; 10790</t>
+          <t>1896; 10939</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>999; 9212</t>
+          <t>1003; 8631</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16227; 31010</t>
+          <t>15906; 30033</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6341</t>
+          <t>0; 7286</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5851</t>
+          <t>0; 4653</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033; 10960</t>
+          <t>1029; 10624</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24556; 44978</t>
+          <t>24868; 45367</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3205; 16246</t>
+          <t>2763; 16124</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2030; 16090</t>
+          <t>2858; 15470</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>901; 7295</t>
+          <t>905; 8271</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2946; 39590</t>
+          <t>3626; 40030</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4600; 20171</t>
+          <t>4348; 19408</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2880; 16751</t>
+          <t>2866; 16047</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2935; 13721</t>
+          <t>3008; 15651</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15948; 84815</t>
+          <t>18598; 85018</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1930</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7796</t>
+          <t>0; 7746</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>807; 7458</t>
+          <t>818; 8097</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8436; 20693</t>
+          <t>8168; 19916</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2013</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1956; 14092</t>
+          <t>2111; 13234</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>981; 10292</t>
+          <t>1017; 10485</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25877; 40273</t>
+          <t>25887; 40619</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1988</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3251; 16932</t>
+          <t>3446; 15631</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2966; 14620</t>
+          <t>2892; 14123</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>36902; 56481</t>
+          <t>37526; 56728</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1879</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1971</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2050</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>707; 12870</t>
+          <t>560; 10633</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 8121</t>
+          <t>0; 6759</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1062; 11003</t>
+          <t>1071; 10714</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1259; 11837</t>
+          <t>1247; 10920</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34455; 52360</t>
+          <t>34967; 52915</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 8101</t>
+          <t>0; 7454</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1052; 9760</t>
+          <t>1054; 9912</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1259; 12051</t>
+          <t>1101; 11206</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>38028; 60136</t>
+          <t>36930; 57693</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5024; 20538</t>
+          <t>5317; 19966</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9457; 26765</t>
+          <t>9727; 28419</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10489; 28411</t>
+          <t>10312; 27270</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>65927; 94730</t>
+          <t>63945; 94704</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10459; 28867</t>
+          <t>10449; 29697</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19003; 40394</t>
+          <t>18639; 42406</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14179; 33959</t>
+          <t>14473; 34139</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>58414; 159121</t>
+          <t>53687; 158506</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18946; 41642</t>
+          <t>18492; 41315</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33055; 63576</t>
+          <t>33322; 62434</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27902; 55169</t>
+          <t>28878; 55665</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>116066; 239701</t>
+          <t>116199; 237819</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R1-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R1-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,13</t>
+          <t>1,14; 6,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,46</t>
+          <t>0,48; 4,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,23; 22,8</t>
+          <t>6,21; 20,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,58</t>
+          <t>0,51; 4,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 7,95</t>
+          <t>1,44; 7,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,67</t>
+          <t>1,39; 6,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,88; 21,72</t>
+          <t>6,48; 20,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,57</t>
+          <t>0,47; 2,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,67</t>
+          <t>1,9; 5,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,27</t>
+          <t>1,35; 4,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,45; 19,25</t>
+          <t>7,66; 16,89</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,07</t>
+          <t>0,83; 7,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -867,52 +867,52 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,64</t>
+          <t>0,39; 3,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 20,62</t>
+          <t>5,12; 18,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,48</t>
+          <t>0,38; 3,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,34</t>
+          <t>0,42; 4,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,87; 24,02</t>
+          <t>9,99; 22,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,02</t>
+          <t>0,65; 3,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,7</t>
+          <t>0,35; 2,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,06</t>
+          <t>0,57; 2,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,31; 19,47</t>
+          <t>9,39; 18,68</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,2</t>
+          <t>0,24; 2,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,09</t>
+          <t>0,31; 2,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,88; 23,77</t>
+          <t>9,19; 22,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,57</t>
+          <t>0,0; 4,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,6; 44,11</t>
+          <t>18,78; 43,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,91</t>
+          <t>0,19; 1,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,85</t>
+          <t>0,32; 1,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,91</t>
+          <t>0,22; 2,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,81; 26,07</t>
+          <t>13,97; 26,67</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,6</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,67</t>
+          <t>0,16; 1,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,01; 25,56</t>
+          <t>12,66; 24,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,43</t>
+          <t>0,71; 3,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,97</t>
+          <t>0,52; 2,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,58</t>
+          <t>0,17; 1,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 11,81</t>
+          <t>7,67; 14,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,56</t>
+          <t>0,31; 1,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,23</t>
+          <t>0,22; 1,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,35</t>
+          <t>0,23; 1,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 16,47</t>
+          <t>11,2; 18,49</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1282,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,15</t>
+          <t>0,21; 2,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,31; 27,57</t>
+          <t>10,2; 25,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,26</t>
+          <t>0,35; 2,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,1</t>
+          <t>0,21; 2,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,25; 22,35</t>
+          <t>12,98; 20,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,24 +1322,24 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,72</t>
+          <t>0,36; 1,8</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,61</t>
+          <t>0,33; 1,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,78; 22,34</t>
+          <t>13,22; 20,17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,09; 58,76</t>
+          <t>2,52; 52,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1447,32 +1447,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,5</t>
+          <t>0,17; 1,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,92; 27,12</t>
+          <t>16,71; 25,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,13</t>
+          <t>0,12; 1,23</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,34</t>
+          <t>0,13; 1,33</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,32; 27,06</t>
+          <t>16,69; 25,63</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,05</t>
+          <t>0,31; 1,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,33</t>
+          <t>0,44; 1,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,44</t>
+          <t>0,54; 1,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,57; 20,1</t>
+          <t>12,43; 18,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,29</t>
+          <t>0,45; 1,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,69</t>
+          <t>0,74; 1,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,47</t>
+          <t>0,61; 1,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,06; 17,9</t>
+          <t>14,61; 18,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,98</t>
+          <t>0,43; 1,01</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,34</t>
+          <t>0,71; 1,35</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,32</t>
+          <t>0,7; 1,35</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,56; 17,53</t>
+          <t>14,4; 17,83</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16945</t>
+          <t>17678</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5240</t>
+          <t>0; 6185</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2946; 15632</t>
+          <t>2898; 16048</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1062; 9763</t>
+          <t>1048; 9709</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4497; 14176</t>
+          <t>4357; 14217</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1024; 11516</t>
+          <t>1043; 10254</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3066; 16440</t>
+          <t>2975; 15063</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2943; 13780</t>
+          <t>2879; 13243</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4952; 15630</t>
+          <t>5168; 16073</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2185; 12558</t>
+          <t>2301; 12575</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8703; 26189</t>
+          <t>8769; 26398</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5710; 18182</t>
+          <t>5736; 18250</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11340; 25823</t>
+          <t>11482; 25333</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10246</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17210</t>
+          <t>18464</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1652; 13902</t>
+          <t>1623; 13822</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 10443</t>
+          <t>0; 10428</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>871; 8326</t>
+          <t>884; 8562</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3525; 11988</t>
+          <t>3315; 11973</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6915</t>
+          <t>0; 7112</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>925; 8257</t>
+          <t>899; 8227</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1024; 10561</t>
+          <t>1021; 11736</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6496; 15808</t>
+          <t>7449; 17035</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2912; 16880</t>
+          <t>2733; 16392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1921; 13713</t>
+          <t>1764; 13958</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2874; 14447</t>
+          <t>2703; 13927</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11544; 24134</t>
+          <t>13084; 26028</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13091</t>
+          <t>13876</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>10791</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>24666</t>
         </is>
       </c>
     </row>
@@ -2343,32 +2343,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6209</t>
+          <t>0; 6326</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>991; 9006</t>
+          <t>969; 8857</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1004; 10195</t>
+          <t>1023; 8937</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8203; 19738</t>
+          <t>8773; 21054</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5757</t>
+          <t>0; 5795</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5252</t>
+          <t>0; 6258</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,27 +2378,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5980; 14177</t>
+          <t>6715; 15676</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>904; 8887</t>
+          <t>894; 8266</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1896; 10939</t>
+          <t>1913; 11010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1003; 8631</t>
+          <t>1005; 9571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15906; 30033</t>
+          <t>18336; 35008</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33318</t>
+          <t>35695</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14294</t>
+          <t>16370</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>47612</t>
+          <t>52065</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7286</t>
+          <t>0; 6322</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4653</t>
+          <t>0; 4344</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1029; 10624</t>
+          <t>1026; 9950</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24868; 45367</t>
+          <t>26096; 49827</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2763; 16124</t>
+          <t>3357; 16338</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2858; 15470</t>
+          <t>2736; 15148</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>905; 8271</t>
+          <t>894; 7761</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3626; 40030</t>
+          <t>11685; 22762</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4348; 19408</t>
+          <t>3888; 18933</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2866; 16047</t>
+          <t>2830; 16811</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3008; 15651</t>
+          <t>2664; 14274</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18598; 85018</t>
+          <t>40146; 66272</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13348</t>
+          <t>13559</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32711</t>
+          <t>34354</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>46059</t>
+          <t>47912</t>
         </is>
       </c>
     </row>
@@ -2764,17 +2764,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7746</t>
+          <t>0; 6744</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>818; 8097</t>
+          <t>803; 7973</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8168; 19916</t>
+          <t>8323; 20767</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2784,17 +2784,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2111; 13234</t>
+          <t>2076; 14054</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1017; 10485</t>
+          <t>1028; 10307</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25887; 40619</t>
+          <t>27287; 42105</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2804,24 +2804,24 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3446; 15631</t>
+          <t>3218; 16297</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2892; 14123</t>
+          <t>2851; 13729</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>37526; 56728</t>
+          <t>38563; 58840</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>42913</t>
+          <t>45747</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>46702</t>
+          <t>49707</t>
         </is>
       </c>
     </row>
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>560; 10633</t>
+          <t>617; 12778</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6759</t>
+          <t>0; 7557</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1071; 10714</t>
+          <t>1056; 10667</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1247; 10920</t>
+          <t>1268; 11487</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34967; 52915</t>
+          <t>37029; 56178</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 7454</t>
+          <t>0; 8751</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1054; 9912</t>
+          <t>1070; 10788</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1101; 11206</t>
+          <t>1117; 11089</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>36930; 57693</t>
+          <t>41061; 63051</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>78781</t>
+          <t>82394</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>118178</t>
+          <t>128099</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>196959</t>
+          <t>210492</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5317; 19966</t>
+          <t>5988; 20440</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9727; 28419</t>
+          <t>9478; 27855</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10312; 27270</t>
+          <t>10286; 27518</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>63945; 94704</t>
+          <t>67444; 100174</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10449; 29697</t>
+          <t>10374; 28567</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18639; 42406</t>
+          <t>18460; 41903</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14473; 34139</t>
+          <t>14240; 34235</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>53687; 158506</t>
+          <t>113138; 144876</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18492; 41315</t>
+          <t>18284; 42304</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33322; 62434</t>
+          <t>32772; 62826</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28878; 55665</t>
+          <t>29707; 56872</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>116199; 237819</t>
+          <t>189635; 234836</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R1-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R1-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
